--- a/data/trans_bre/P8_1_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P8_1_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 10,45</t>
+          <t>1,27; 10,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 5,44</t>
+          <t>-4,6; 5,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 6,75</t>
+          <t>-3,34; 6,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 8,15</t>
+          <t>1,37; 7,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 143,48</t>
+          <t>11,0; 154,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 62,66</t>
+          <t>-34,23; 62,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 86,53</t>
+          <t>-26,39; 83,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,07; 139,42</t>
+          <t>13,45; 127,83</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 4,15</t>
+          <t>-3,08; 4,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 4,25</t>
+          <t>-6,42; 3,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 5,0</t>
+          <t>-4,04; 5,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 6,53</t>
+          <t>-1,34; 7,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,87; 108,26</t>
+          <t>-42,6; 121,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,78; 47,38</t>
+          <t>-43,89; 40,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 61,45</t>
+          <t>-33,32; 67,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 68,9</t>
+          <t>-9,76; 74,78</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 19,94</t>
+          <t>5,98; 19,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 14,97</t>
+          <t>1,93; 15,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 16,86</t>
+          <t>1,57; 17,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 12,99</t>
+          <t>-53,4; 13,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,81; 198,74</t>
+          <t>43,91; 193,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,59; 96,96</t>
+          <t>9,06; 95,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 131,75</t>
+          <t>9,61; 137,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-69,81; 80,47</t>
+          <t>-71,13; 80,97</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,71</t>
+          <t>0,61; 7,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 2,62</t>
+          <t>-4,97; 2,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,5</t>
+          <t>-2,74; 4,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,71; -1,33</t>
+          <t>-12,72; -1,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 57,9</t>
+          <t>3,88; 58,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 17,47</t>
+          <t>-26,56; 16,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 32,67</t>
+          <t>-16,56; 30,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,08; -7,54</t>
+          <t>-62,48; -7,97</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 10,29</t>
+          <t>0,35; 10,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 21,29</t>
+          <t>11,59; 21,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 12,95</t>
+          <t>3,93; 13,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 10,13</t>
+          <t>-3,19; 10,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 90,91</t>
+          <t>0,86; 86,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,0; 146,55</t>
+          <t>55,75; 143,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,71; 71,73</t>
+          <t>18,01; 75,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 54,49</t>
+          <t>-11,91; 57,17</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,03; 30,14</t>
+          <t>23,67; 30,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,32; 34,46</t>
+          <t>26,56; 34,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,13; 31,45</t>
+          <t>24,2; 31,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,8; 33,25</t>
+          <t>26,96; 33,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>517,18; 2807,74</t>
+          <t>516,68; 2285,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>392,57; 1949,95</t>
+          <t>409,51; 1897,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>532,69; 3549,0</t>
+          <t>556,31; 3638,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>788,94; 5683,95</t>
+          <t>775,94; 4707,99</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,52; 11,96</t>
+          <t>8,48; 12,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,61; 12,57</t>
+          <t>8,71; 12,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,65</t>
+          <t>6,75; 10,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 6,8</t>
+          <t>-18,84; 7,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,74; 116,13</t>
+          <t>70,85; 115,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,76; 92,35</t>
+          <t>56,11; 92,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,07; 81,2</t>
+          <t>45,44; 81,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-48,67; 46,93</t>
+          <t>-49,45; 50,73</t>
         </is>
       </c>
     </row>
